--- a/public/templates/template_performance_dialog.xlsx
+++ b/public/templates/template_performance_dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\01126010010\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\kpn-pm-cg\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>due_date</t>
-  </si>
-  <si>
-    <t>type_name</t>
   </si>
   <si>
     <t>status</t>
@@ -128,6 +125,9 @@
   </si>
   <si>
     <t>00000000002</t>
+  </si>
+  <si>
+    <t>objectives</t>
   </si>
 </sst>
 </file>
@@ -1029,67 +1029,67 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="N1" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="D2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="G2" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" s="6">
         <v>2026</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N2" s="8"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1099,15 +1099,15 @@
         <v>2026</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
